--- a/data/trans_orig/P37A$medicoenfermedad-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P37A$medicoenfermedad-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21129</t>
+          <t>21832</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>808</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>8651</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8599</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25156</t>
+          <t>23881</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452647</t>
+          <t>451944</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>467279</t>
+          <t>467622</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298536</t>
+          <t>298029</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>305880</t>
+          <t>305872</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>755301</t>
+          <t>756576</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>771858</t>
+          <t>772070</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17698</t>
+          <t>17203</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11278</t>
+          <t>11495</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8611</t>
+          <t>8587</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23880</t>
+          <t>24938</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>349236</t>
+          <t>349731</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>362432</t>
+          <t>362336</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>360587</t>
+          <t>360370</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369903</t>
+          <t>369885</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>714919</t>
+          <t>713861</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>730188</t>
+          <t>730212</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26644</t>
+          <t>26478</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>11252</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13984</t>
+          <t>13067</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33888</t>
+          <t>33999</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>515745</t>
+          <t>515911</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>533908</t>
+          <t>533390</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155366</t>
+          <t>156530</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165813</t>
+          <t>165944</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>676283</t>
+          <t>676172</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>696187</t>
+          <t>697104</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46288</t>
+          <t>45573</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74896</t>
+          <t>74381</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>19189</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38812</t>
+          <t>37547</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,47 +1812,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>85966</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>70611</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>106123</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>5,43%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>85966</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>70821</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>107421</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1163438</t>
+          <t>1163953</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1192046</t>
+          <t>1192761</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>675473</t>
+          <t>676738</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>696584</t>
+          <t>695096</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,47 +1925,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>94,74%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>97,31%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1829</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1866654</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1846497</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1882009</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>95,6%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>94,57%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>97,52%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1866654</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1845199</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1881799</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>95,6%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>94,5%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17601</t>
+          <t>18546</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10740</t>
+          <t>10913</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27023</t>
+          <t>27916</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19412</t>
+          <t>19714</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41201</t>
+          <t>42316</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>332954</t>
+          <t>332009</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>344939</t>
+          <t>344561</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>541729</t>
+          <t>540836</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>558012</t>
+          <t>557839</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>878106</t>
+          <t>876991</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>899895</t>
+          <t>899593</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10667</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26677</t>
+          <t>25139</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49201</t>
+          <t>49164</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30311</t>
+          <t>29351</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55257</t>
+          <t>54702</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>287839</t>
+          <t>287534</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>296342</t>
+          <t>296345</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1199559</t>
+          <t>1199596</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1222083</t>
+          <t>1223621</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1491703</t>
+          <t>1492258</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1516649</t>
+          <t>1517609</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94641</t>
+          <t>93200</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>134826</t>
+          <t>135831</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>75466</t>
+          <t>76013</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>112784</t>
+          <t>114496</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>178702</t>
+          <t>180921</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>234874</t>
+          <t>238399</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3135364</t>
+          <t>3134359</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3175549</t>
+          <t>3176990</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3265340</t>
+          <t>3263628</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3302658</t>
+          <t>3302111</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6413440</t>
+          <t>6409915</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6469612</t>
+          <t>6467393</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16850</t>
+          <t>17933</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>5895</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20900</t>
+          <t>19454</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>11474</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30590</t>
+          <t>30052</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>420361</t>
+          <t>419278</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>434049</t>
+          <t>434102</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>293554</t>
+          <t>295000</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>308873</t>
+          <t>308559</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>721075</t>
+          <t>721613</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>740267</t>
+          <t>740191</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18337</t>
+          <t>17240</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15465</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7947</t>
+          <t>7938</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26677</t>
+          <t>26035</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>400460</t>
+          <t>401557</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>414684</t>
+          <t>415629</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>322546</t>
+          <t>322715</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336056</t>
+          <t>335338</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>730131</t>
+          <t>730773</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>748861</t>
+          <t>748870</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24982</t>
+          <t>24227</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51481</t>
+          <t>49479</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11955</t>
+          <t>11923</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30820</t>
+          <t>30742</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58464</t>
+          <t>58326</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>577934</t>
+          <t>579936</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>604433</t>
+          <t>605188</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>248174</t>
+          <t>248206</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>258054</t>
+          <t>258168</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>831080</t>
+          <t>831218</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>858724</t>
+          <t>858802</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36056</t>
+          <t>36587</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64102</t>
+          <t>64528</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17392</t>
+          <t>17517</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39558</t>
+          <t>38016</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60137</t>
+          <t>60883</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94945</t>
+          <t>94061</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1094907</t>
+          <t>1094481</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1122953</t>
+          <t>1122422</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>727099</t>
+          <t>728641</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>749265</t>
+          <t>749140</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1830722</t>
+          <t>1831606</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1865530</t>
+          <t>1864784</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21994</t>
+          <t>22471</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17434</t>
+          <t>18651</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38311</t>
+          <t>39897</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,47 +4790,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>40289</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>29116</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>53863</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>2,29%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>40289</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>28879</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>53303</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>488602</t>
+          <t>488125</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>502767</t>
+          <t>503286</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>723211</t>
+          <t>721625</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>744088</t>
+          <t>742871</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,47 +4903,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>97,55%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1151</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1231829</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1218255</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1243002</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>96,83%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>95,77%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>97,71%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1151</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1231829</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1218815</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1243239</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>96,83%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>95,81%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3811</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>15773</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48721</t>
+          <t>49105</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>80616</t>
+          <t>81359</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56502</t>
+          <t>55317</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>89079</t>
+          <t>91125</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251215</t>
+          <t>251109</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263723</t>
+          <t>263071</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1028735</t>
+          <t>1027992</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1060630</t>
+          <t>1060246</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1287154</t>
+          <t>1285108</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1319731</t>
+          <t>1320916</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>104012</t>
+          <t>101441</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>149929</t>
+          <t>147356</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>120414</t>
+          <t>118580</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>168393</t>
+          <t>166278</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>237037</t>
+          <t>234282</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>303710</t>
+          <t>298788</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3271981</t>
+          <t>3274554</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3317898</t>
+          <t>3320469</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3381732</t>
+          <t>3383847</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3429711</t>
+          <t>3431545</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6668325</t>
+          <t>6673247</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6734998</t>
+          <t>6737753</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>6901</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20457</t>
+          <t>21349</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14114</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11952</t>
+          <t>11832</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30418</t>
+          <t>29775</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>408635</t>
+          <t>407743</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>422672</t>
+          <t>422191</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>332941</t>
+          <t>331496</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>343954</t>
+          <t>344069</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>745729</t>
+          <t>746372</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>764195</t>
+          <t>764315</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16905</t>
+          <t>16189</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21207</t>
+          <t>21091</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13045</t>
+          <t>13091</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33195</t>
+          <t>32666</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>360322</t>
+          <t>361038</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>373424</t>
+          <t>373394</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>351066</t>
+          <t>351182</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>366165</t>
+          <t>365696</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>716305</t>
+          <t>716834</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>736455</t>
+          <t>736409</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16432</t>
+          <t>16456</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36027</t>
+          <t>36351</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10568</t>
+          <t>11381</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18765</t>
+          <t>19399</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41611</t>
+          <t>41992</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>485887</t>
+          <t>485563</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>505482</t>
+          <t>505458</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155555</t>
+          <t>154742</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165076</t>
+          <t>165083</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>646425</t>
+          <t>646044</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>669271</t>
+          <t>668637</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36831</t>
+          <t>36739</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65662</t>
+          <t>65232</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11338</t>
+          <t>11443</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29203</t>
+          <t>28580</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53842</t>
+          <t>53184</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85871</t>
+          <t>86966</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1083976</t>
+          <t>1084406</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1112807</t>
+          <t>1112899</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>796673</t>
+          <t>797296</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>814538</t>
+          <t>814433</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1889643</t>
+          <t>1888548</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1921672</t>
+          <t>1922330</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9806</t>
+          <t>10391</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26005</t>
+          <t>27669</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19606</t>
+          <t>19534</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41505</t>
+          <t>40999</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34118</t>
+          <t>33995</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61020</t>
+          <t>60705</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>594701</t>
+          <t>593037</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>610900</t>
+          <t>610315</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>696739</t>
+          <t>697245</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>718638</t>
+          <t>718710</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1297930</t>
+          <t>1298245</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1324832</t>
+          <t>1324955</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13373</t>
+          <t>13970</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22946</t>
+          <t>21915</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47700</t>
+          <t>47000</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27850</t>
+          <t>26503</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>53938</t>
+          <t>54429</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>273772</t>
+          <t>273175</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>285110</t>
+          <t>285087</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1034325</t>
+          <t>1035025</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1059079</t>
+          <t>1060110</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1315232</t>
+          <t>1314741</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1341320</t>
+          <t>1342667</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>96755</t>
+          <t>95880</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>140143</t>
+          <t>140714</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>85285</t>
+          <t>86105</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>127983</t>
+          <t>128694</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>191675</t>
+          <t>195334</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>252887</t>
+          <t>254091</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3245579</t>
+          <t>3245008</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3288967</t>
+          <t>3289842</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3403613</t>
+          <t>3402902</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3446311</t>
+          <t>3445491</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6664431</t>
+          <t>6663227</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6725643</t>
+          <t>6721984</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>23807</t>
+          <t>28981</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16391</t>
+          <t>20478</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33376</t>
+          <t>41412</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21091</t>
+          <t>23496</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14621</t>
+          <t>16382</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30255</t>
+          <t>32447</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>44899</t>
+          <t>52477</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35141</t>
+          <t>41344</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57888</t>
+          <t>65949</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>481405</t>
+          <t>521637</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>471836</t>
+          <t>509206</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>488821</t>
+          <t>530140</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>426376</t>
+          <t>464915</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>417212</t>
+          <t>455964</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>432846</t>
+          <t>472029</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>907780</t>
+          <t>986552</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>894791</t>
+          <t>973080</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>917538</t>
+          <t>997685</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,17 +8976,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21712</t>
+          <t>23208</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14965</t>
+          <t>15136</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31346</t>
+          <t>33520</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29747</t>
+          <t>32610</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22517</t>
+          <t>24762</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40498</t>
+          <t>43464</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,17 +9046,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>51460</t>
+          <t>55818</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40825</t>
+          <t>43279</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65977</t>
+          <t>70599</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -9089,17 +9089,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>430501</t>
+          <t>460004</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>420867</t>
+          <t>449692</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>437248</t>
+          <t>468076</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>352833</t>
+          <t>390533</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>342082</t>
+          <t>379679</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>360063</t>
+          <t>398381</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,17 +9159,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>783333</t>
+          <t>850537</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>768816</t>
+          <t>835756</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>793968</t>
+          <t>863076</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>24604</t>
+          <t>25746</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8232</t>
+          <t>16351</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43849</t>
+          <t>35292</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,22 +9354,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11576</t>
+          <t>12463</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17317</t>
+          <t>19451</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>36180</t>
+          <t>38210</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15212</t>
+          <t>29053</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54637</t>
+          <t>49541</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>643660</t>
+          <t>445866</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>624415</t>
+          <t>436320</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>660032</t>
+          <t>455261</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,22 +9467,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>155335</t>
+          <t>175034</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149594</t>
+          <t>168046</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159588</t>
+          <t>179261</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>798995</t>
+          <t>620899</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>780538</t>
+          <t>609568</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>819963</t>
+          <t>630056</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>74047</t>
+          <t>79630</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59238</t>
+          <t>63675</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93878</t>
+          <t>100594</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26474</t>
+          <t>30832</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13818</t>
+          <t>23223</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37787</t>
+          <t>40404</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>100521</t>
+          <t>110462</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69693</t>
+          <t>93642</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122692</t>
+          <t>131351</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>960772</t>
+          <t>1052213</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>940941</t>
+          <t>1031249</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>975581</t>
+          <t>1068168</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>951620</t>
+          <t>830379</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>940307</t>
+          <t>820807</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>964276</t>
+          <t>837988</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1912391</t>
+          <t>1882592</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1890220</t>
+          <t>1861703</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1943219</t>
+          <t>1899412</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>29971</t>
+          <t>32635</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22123</t>
+          <t>23421</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40566</t>
+          <t>43607</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>48728</t>
+          <t>55986</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34871</t>
+          <t>45221</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63501</t>
+          <t>69851</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>78699</t>
+          <t>88621</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61172</t>
+          <t>74190</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95301</t>
+          <t>107872</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>445075</t>
+          <t>535329</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>434480</t>
+          <t>524357</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>452923</t>
+          <t>544543</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>792607</t>
+          <t>774864</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>777834</t>
+          <t>760999</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>806464</t>
+          <t>785629</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1237682</t>
+          <t>1310193</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1221080</t>
+          <t>1290942</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1255209</t>
+          <t>1324624</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>94,7%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2981</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>696</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8004</t>
+          <t>7559</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>69968</t>
+          <t>77404</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59301</t>
+          <t>65030</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82625</t>
+          <t>90540</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>72948</t>
+          <t>80310</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>61320</t>
+          <t>67425</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>86647</t>
+          <t>95243</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>237526</t>
+          <t>234321</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>232503</t>
+          <t>229669</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239595</t>
+          <t>236532</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>691403</t>
+          <t>766877</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>678746</t>
+          <t>753741</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>779251</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>928930</t>
+          <t>1001199</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>915231</t>
+          <t>986266</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>940558</t>
+          <t>1014084</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,77%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>177122</t>
+          <t>193108</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>138618</t>
+          <t>169534</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>206542</t>
+          <t>219528</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>207584</t>
+          <t>232791</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>169834</t>
+          <t>208818</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>235063</t>
+          <t>257201</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>384706</t>
+          <t>425899</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>329708</t>
+          <t>394009</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>425509</t>
+          <t>465824</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3198938</t>
+          <t>3249368</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3169518</t>
+          <t>3222948</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3237442</t>
+          <t>3272942</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3370174</t>
+          <t>3402602</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3342695</t>
+          <t>3378192</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3407924</t>
+          <t>3426575</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6569112</t>
+          <t>6651970</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6528309</t>
+          <t>6612045</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6624110</t>
+          <t>6683860</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
